--- a/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt2_rubricas.xlsx
@@ -1968,13 +1968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96C677B1-1977-4743-8F7F-365BF68B5F99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FE39177-9614-448F-BEEF-8AEF53BBC29E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8EEF091-62F2-4C18-B9BB-664677C105BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CAE3279-D92A-481B-9228-6BCB25138309}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70E7C064-7DCD-41DA-8CB5-F3F2E5976998}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F3349F-E6A1-4C57-AA24-309C971FD200}"/>
 </file>